--- a/stacked_model/results/validation/deployed_stack_config/deployed_stack_summary.xlsx
+++ b/stacked_model/results/validation/deployed_stack_config/deployed_stack_summary.xlsx
@@ -583,7 +583,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
@@ -592,40 +592,40 @@
         <v>1900</v>
       </c>
       <c r="H2" t="n">
-        <v>3.620806820402495</v>
+        <v>3.549476959456683</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7392115055151569</v>
+        <v>0.700393281697821</v>
       </c>
       <c r="J2" t="n">
-        <v>5.571422254688597</v>
+        <v>5.424563677194251</v>
       </c>
       <c r="K2" t="n">
-        <v>1.78633451366268</v>
+        <v>1.548759074098645</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8252665079868968</v>
+        <v>0.8354949926068899</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1158975672937242</v>
+        <v>0.09755652573837309</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8568421052631578</v>
+        <v>0.8210526315789474</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05347339665171293</v>
+        <v>0.06682852945350067</v>
       </c>
       <c r="P2" t="n">
-        <v>3.075732925591151</v>
+        <v>3.164455951946408</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3682781154727561</v>
+        <v>0.4448475198790096</v>
       </c>
       <c r="R2" t="n">
-        <v>-172.1552365123595</v>
+        <v>-172.2415354370157</v>
       </c>
       <c r="S2" t="n">
-        <v>9.987295399096116</v>
+        <v>10.25839242575567</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
